--- a/untranslated/downloads/data-excel/8.10.2.xlsx
+++ b/untranslated/downloads/data-excel/8.10.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -366,7 +366,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -484,6 +484,28 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -518,7 +540,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -581,6 +603,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal 17" xfId="1"/>
@@ -8397,14 +8424,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="44" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -8415,7 +8442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>26</v>
       </c>
@@ -8426,7 +8453,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -8436,8 +8463,9 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>109</v>
       </c>
@@ -8465,8 +8493,11 @@
       <c r="I4" s="24">
         <v>2023</v>
       </c>
+      <c r="J4" s="24">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>28</v>
       </c>
@@ -8494,8 +8525,11 @@
       <c r="I5" s="18">
         <v>45.949580055212706</v>
       </c>
+      <c r="J5" s="28">
+        <v>58.8</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>30</v>
       </c>
@@ -8511,8 +8545,9 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
     </row>
-    <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>31</v>
       </c>
@@ -8540,8 +8575,11 @@
       <c r="I7" s="21">
         <v>50.315128678474018</v>
       </c>
+      <c r="J7" s="29">
+        <v>62.1</v>
+      </c>
     </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>32</v>
       </c>
@@ -8569,8 +8607,11 @@
       <c r="I8" s="21">
         <v>43.219999170895854</v>
       </c>
+      <c r="J8" s="29">
+        <v>56</v>
+      </c>
     </row>
-    <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>103</v>
       </c>
@@ -8586,8 +8627,9 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
     </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>36</v>
       </c>
@@ -8615,8 +8657,11 @@
       <c r="I10" s="21">
         <v>44.415417641633219</v>
       </c>
+      <c r="J10" s="29">
+        <v>58</v>
+      </c>
     </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>37</v>
       </c>
@@ -8644,8 +8689,11 @@
       <c r="I11" s="21">
         <v>47.251391232382026</v>
       </c>
+      <c r="J11" s="29">
+        <v>59.5</v>
+      </c>
     </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>40</v>
       </c>
@@ -8661,8 +8709,9 @@
       <c r="G12" s="20"/>
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
     </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>41</v>
       </c>
@@ -8690,8 +8739,11 @@
       <c r="I13" s="21">
         <v>41.667810195049299</v>
       </c>
+      <c r="J13" s="29">
+        <v>52.7</v>
+      </c>
     </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>44</v>
       </c>
@@ -8719,8 +8771,11 @@
       <c r="I14" s="21">
         <v>41.486441621675908</v>
       </c>
+      <c r="J14" s="29">
+        <v>48.4</v>
+      </c>
     </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>47</v>
       </c>
@@ -8748,8 +8803,11 @@
       <c r="I15" s="21">
         <v>52.909628957776725</v>
       </c>
+      <c r="J15" s="29">
+        <v>64.5</v>
+      </c>
     </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>50</v>
       </c>
@@ -8777,8 +8835,11 @@
       <c r="I16" s="21">
         <v>62.574019909498347</v>
       </c>
+      <c r="J16" s="29">
+        <v>68</v>
+      </c>
     </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>53</v>
       </c>
@@ -8806,8 +8867,11 @@
       <c r="I17" s="21">
         <v>50.089746706331191</v>
       </c>
+      <c r="J17" s="29">
+        <v>69.3</v>
+      </c>
     </row>
-    <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>56</v>
       </c>
@@ -8835,8 +8899,11 @@
       <c r="I18" s="21">
         <v>44.864451548602972</v>
       </c>
+      <c r="J18" s="29">
+        <v>58.8</v>
+      </c>
     </row>
-    <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>59</v>
       </c>
@@ -8864,8 +8931,11 @@
       <c r="I19" s="21">
         <v>35.967162950905177</v>
       </c>
+      <c r="J19" s="29">
+        <v>45</v>
+      </c>
     </row>
-    <row r="20" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>62</v>
       </c>
@@ -8893,8 +8963,11 @@
       <c r="I20" s="21">
         <v>47.2422482593567</v>
       </c>
+      <c r="J20" s="29">
+        <v>62.2</v>
+      </c>
     </row>
-    <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>65</v>
       </c>
@@ -8922,8 +8995,11 @@
       <c r="I21" s="21">
         <v>57.053084433540945</v>
       </c>
+      <c r="J21" s="29">
+        <v>73.5</v>
+      </c>
     </row>
-    <row r="22" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>104</v>
       </c>
@@ -8939,8 +9015,9 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
     </row>
-    <row r="23" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>68</v>
       </c>
@@ -8968,8 +9045,11 @@
       <c r="I23" s="21">
         <v>23.872922810126894</v>
       </c>
+      <c r="J23" s="29">
+        <v>32.799999999999997</v>
+      </c>
     </row>
-    <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>92</v>
       </c>
@@ -8997,8 +9077,11 @@
       <c r="I24" s="21">
         <v>48.27741695137928</v>
       </c>
+      <c r="J24" s="29">
+        <v>63.2</v>
+      </c>
     </row>
-    <row r="25" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>93</v>
       </c>
@@ -9026,8 +9109,11 @@
       <c r="I25" s="21">
         <v>69.7146568327408</v>
       </c>
+      <c r="J25" s="29">
+        <v>80.400000000000006</v>
+      </c>
     </row>
-    <row r="26" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
         <v>105</v>
       </c>
@@ -9043,8 +9129,9 @@
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
     </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>70</v>
       </c>
@@ -9072,8 +9159,11 @@
       <c r="I27" s="21">
         <v>21.77710692964105</v>
       </c>
+      <c r="J27" s="29">
+        <v>27</v>
+      </c>
     </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>71</v>
       </c>
@@ -9101,8 +9191,11 @@
       <c r="I28" s="21">
         <v>24.756440351891371</v>
       </c>
+      <c r="J28" s="29">
+        <v>30.5</v>
+      </c>
     </row>
-    <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>72</v>
       </c>
@@ -9130,8 +9223,11 @@
       <c r="I29" s="21">
         <v>41.781082603975655</v>
       </c>
+      <c r="J29" s="29">
+        <v>57.2</v>
+      </c>
     </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>73</v>
       </c>
@@ -9159,8 +9255,11 @@
       <c r="I30" s="21">
         <v>55.952587531016164</v>
       </c>
+      <c r="J30" s="29">
+        <v>69.099999999999994</v>
+      </c>
     </row>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>74</v>
       </c>
@@ -9188,8 +9287,11 @@
       <c r="I31" s="21">
         <v>65.760347501612472</v>
       </c>
+      <c r="J31" s="29">
+        <v>77.3</v>
+      </c>
     </row>
-    <row r="32" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>80</v>
       </c>
@@ -9205,8 +9307,9 @@
       <c r="G32" s="21"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
+      <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>75</v>
       </c>
@@ -9235,8 +9338,11 @@
       <c r="I33" s="26">
         <v>36.943115111698582</v>
       </c>
+      <c r="J33" s="30">
+        <v>48.5</v>
+      </c>
     </row>
-    <row r="34" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>76</v>
       </c>
@@ -9265,8 +9371,11 @@
       <c r="I34" s="26">
         <v>43.758492476090815</v>
       </c>
+      <c r="J34" s="30">
+        <v>55.8</v>
+      </c>
     </row>
-    <row r="35" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>77</v>
       </c>
@@ -9295,8 +9404,11 @@
       <c r="I35" s="26">
         <v>45.502117000636005</v>
       </c>
+      <c r="J35" s="30">
+        <v>57.7</v>
+      </c>
     </row>
-    <row r="36" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>78</v>
       </c>
@@ -9325,8 +9437,11 @@
       <c r="I36" s="26">
         <v>47.36993563223902</v>
       </c>
+      <c r="J36" s="30">
+        <v>62.3</v>
+      </c>
     </row>
-    <row r="37" spans="1:9" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>79</v>
       </c>
@@ -9355,8 +9470,11 @@
       <c r="I37" s="25">
         <v>52.665872825774791</v>
       </c>
+      <c r="J37" s="25">
+        <v>65.3</v>
+      </c>
     </row>
-    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
         <v>87</v>
       </c>
